--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS GENERAL SEASON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS GENERAL SEASON.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$113</definedName>
@@ -861,7 +861,11 @@
           <t>49.2</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -1206,7 +1210,11 @@
           <t>44.5</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -1275,7 +1283,11 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -1344,7 +1356,11 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -1413,7 +1429,11 @@
           <t>62.8</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -1482,7 +1502,11 @@
           <t>38.5</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -1620,7 +1644,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -1689,7 +1717,11 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -1896,7 +1928,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -1965,7 +2001,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2034,7 +2074,11 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>6.1</t>
@@ -2172,7 +2216,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -2241,7 +2289,11 @@
           <t>71.1</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -2310,7 +2362,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -2379,7 +2435,11 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2448,7 +2508,11 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
           <t>6.7</t>
@@ -2517,7 +2581,11 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2724,7 +2792,11 @@
           <t>63.6</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -2793,7 +2865,11 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -3069,7 +3145,11 @@
           <t>36.8</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -3138,7 +3218,11 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3207,7 +3291,11 @@
           <t>77.6</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -3276,7 +3364,11 @@
           <t>39.1</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -3345,7 +3437,11 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -3414,7 +3510,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -3483,7 +3583,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -3552,7 +3656,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -3621,7 +3729,11 @@
           <t>21.7</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -3690,7 +3802,11 @@
           <t>24.4</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -3759,7 +3875,11 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -3828,7 +3948,11 @@
           <t>69.1</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -3966,7 +4090,11 @@
           <t>31.6</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
           <t>8.5</t>
@@ -4035,7 +4163,11 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -4104,7 +4236,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -4173,7 +4309,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
           <t>7.7</t>
@@ -4242,7 +4382,11 @@
           <t>47.4</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -4380,7 +4524,11 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="N56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
           <t>8.2</t>
@@ -4449,7 +4597,11 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -4587,7 +4739,11 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -4656,7 +4812,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -4725,7 +4885,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -4932,7 +5096,11 @@
           <t>45.9</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -5001,7 +5169,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
           <t>14.5</t>
@@ -5070,7 +5242,11 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -5123,7 +5299,11 @@
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="28" customHeight="1">
@@ -5245,7 +5425,11 @@
           <t>42.3</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -5314,7 +5498,11 @@
           <t>37.9</t>
         </is>
       </c>
-      <c r="N70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -5383,7 +5571,11 @@
           <t>57.6</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -5452,7 +5644,11 @@
           <t>78.1</t>
         </is>
       </c>
-      <c r="N72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -5728,7 +5924,11 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -5866,7 +6066,11 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
           <t>6.2</t>
@@ -5935,7 +6139,11 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -6004,7 +6212,11 @@
           <t>47.7</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -6073,7 +6285,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -6142,7 +6358,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
           <t>6.3</t>
@@ -6211,7 +6431,11 @@
           <t>17.4</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -6280,7 +6504,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -6349,7 +6577,11 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -6418,7 +6650,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -6536,7 +6772,11 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
-      <c r="N88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O88" s="3" t="inlineStr"/>
     </row>
     <row r="89" ht="28" customHeight="1">
@@ -8099,7 +8339,11 @@
           <t>91.4</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -8168,7 +8412,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -8237,7 +8485,11 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="N113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O113" s="5" t="inlineStr">
         <is>
           <t>5.8</t>
